--- a/sample-data/split/Itinerary.xlsx
+++ b/sample-data/split/Itinerary.xlsx
@@ -56,13 +56,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -466,307 +463,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Day 1</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>10:30 PM</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Depart Mumbai Central by MMCT Jaipur SF</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Mumbai Central</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Day 2</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Afternoon</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Arrive Jaipur, check in, orientation walk</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Day 3</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Full day</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Amer Fort, Jantar Mantar and stepwell study</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Day 4</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Morning</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Chand Baori stepwell measurement exercise</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Abhaneri</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Day 5</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Dawn</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Ranthambore safari and habitat mapping</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ranthambore</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Day 6</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Full day</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Project work and presentations at camp</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Ranthambore</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Grade 7</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Day 7</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>8:20 PM</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Board JP BDTS Express for return</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Jaipur</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Day 1</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>7:00 AM</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Coach departs school, breakfast en route</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>School</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Day 2</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>6:00 AM</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sunrise boat survey and bird count</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Sundarbans</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Day 3</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Full day</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Mangrove walk and sketching session</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Sundarbans</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Grade 5</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Day 4</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>2:00 PM</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Return coach to school</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Sundarbans</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
-      <formula1>"JK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Unrecognised grade" error="Pick a grade from the list. A different spelling makes the row disappear from the site." type="list">
+      <formula1>"JK,SK,Grade 1,Grade 2,Grade 3,Grade 4,Grade 5,Grade 6,Grade 7,Grade 8,Grade 9,Grade 10,Grade 11,Grade 12"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
